--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487691_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487691_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5389</v>
+        <v>9.1769</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6114</v>
+        <v>9.331099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0725</v>
+        <v>-0.1542</v>
       </c>
       <c r="G2" t="n">
         <v>7.928</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7288</v>
+        <v>0.3668</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6397</v>
+        <v>0.3594</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0891</v>
+        <v>0.0073</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4064</v>
+        <v>3.6033</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9856</v>
+        <v>4.0461</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5792</v>
+        <v>-0.4429</v>
       </c>
       <c r="G3" t="n">
         <v>1.2249</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0785</v>
+        <v>0.1183</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3017</v>
+        <v>-0.2412</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2232</v>
+        <v>0.3595</v>
       </c>
       <c r="V3" t="n">
         <v>1.2898</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9699</v>
+        <v>3.5643</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7176</v>
+        <v>2.3392</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2523</v>
+        <v>1.2251</v>
       </c>
       <c r="G4" t="n">
         <v>3.3403</v>
@@ -766,13 +766,13 @@
         <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5644</v>
+        <v>0.03</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0902</v>
+        <v>-0.4686</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5258</v>
+        <v>0.4986</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6517</v>
+        <v>3.4913</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7153</v>
+        <v>2.3369</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9364</v>
+        <v>1.1545</v>
       </c>
       <c r="G5" t="n">
         <v>0.9278999999999999</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8001</v>
+        <v>0.0395</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2113</v>
+        <v>-0.5897</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4112</v>
+        <v>0.6292</v>
       </c>
       <c r="V5" t="n">
         <v>1.5537</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2107</v>
+        <v>2.2636</v>
       </c>
       <c r="E6" t="n">
-        <v>1.622</v>
+        <v>1.815</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5887</v>
+        <v>0.4485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.923</v>
+        <v>1.5101</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5454</v>
+        <v>0.0091</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3776</v>
+        <v>1.501</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0349</v>
+        <v>2.6637</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3048</v>
+        <v>0.7456</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3397</v>
+        <v>1.9181</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1119</v>
+        <v>-1.1537</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8502</v>
+        <v>-0.7366</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9621</v>
+        <v>-0.4171</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5336</v>
+        <v>-0.0241</v>
       </c>
       <c r="T6" t="n">
-        <v>0.305</v>
+        <v>-0.5502</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2286</v>
+        <v>0.526</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2161</v>
+        <v>1.5537</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>1.8358</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4982</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4873</v>
+        <v>1.5192</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0933</v>
+        <v>-0.1615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.394</v>
+        <v>1.6807</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5101</v>
+        <v>0.7085</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0091</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.501</v>
+        <v>0.1335</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6637</v>
+        <v>0.0412</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7456</v>
+        <v>0.0412</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9181</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1537</v>
+        <v>0.6673</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7366</v>
+        <v>0.5339</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4171</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8004</v>
+        <v>-0.1091</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2719</v>
+        <v>-0.2027</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4715</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5537</v>
+        <v>0.7257</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2828</v>
+        <v>1.4466</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2616</v>
+        <v>1.0214</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5444</v>
+        <v>0.4252</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7085</v>
+        <v>0.923</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.5454</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1335</v>
+        <v>0.3776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0412</v>
+        <v>1.0349</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0412</v>
+        <v>-0.3048</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3397</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6673</v>
+        <v>-0.1119</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5339</v>
+        <v>0.8502</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>-0.9621</v>
       </c>
       <c r="P8" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3454</v>
+        <v>-0.2305</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>-0.2956</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0426</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7257</v>
+        <v>-0.2161</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7257</v>
+        <v>-0.4982</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7866</v>
+        <v>-0.1894</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.3832</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7089</v>
+        <v>-0.5726</v>
       </c>
       <c r="G9" t="n">
         <v>0.4591</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7099</v>
+        <v>-0.1127</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6057</v>
+        <v>-0.1447</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1043</v>
+        <v>0.032</v>
       </c>
       <c r="V9" t="n">
         <v>-1.506</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4555</v>
+        <v>-1.3187</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8708</v>
+        <v>-0.5705</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5847</v>
+        <v>-0.7482</v>
       </c>
       <c r="G10" t="n">
         <v>0.2365</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3401</v>
+        <v>-0.2033</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0372</v>
+        <v>-0.2007</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1579</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3229</v>
+        <v>-2.0682</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6775</v>
+        <v>-1.4773</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6454</v>
+        <v>-0.5909</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9192</v>
@@ -1312,13 +1312,13 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1577</v>
+        <v>0.097</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2057</v>
+        <v>0.2602</v>
       </c>
       <c r="V11" t="n">
         <v>-1.44</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4928</v>
+        <v>-3.2653</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9453</v>
+        <v>-2.7451</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5475</v>
+        <v>-0.5202</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8706</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.952</v>
+        <v>-0.7245</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6057</v>
+        <v>-0.4055</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3463</v>
+        <v>-0.3191</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2126</v>
+        <v>-5.3405</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3769</v>
+        <v>-5.1777</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1643</v>
+        <v>-0.1628</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5942</v>
@@ -1468,13 +1468,13 @@
         <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5159</v>
+        <v>0.3881</v>
       </c>
       <c r="T13" t="n">
-        <v>0.729</v>
+        <v>-0.0718</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7869</v>
+        <v>0.4599</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8358</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.2773</v>
+        <v>12.8831</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5354</v>
+        <v>11.1408</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7419</v>
+        <v>1.7422</v>
       </c>
       <c r="G14" t="n">
         <v>13.8743</v>
@@ -1546,13 +1546,13 @@
         <v>10.6717</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9702</v>
+        <v>-0.3645000000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.3818</v>
+        <v>-2.7763</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4116</v>
+        <v>2.4117</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5971</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0023</v>
+        <v>2.7486</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7561</v>
+        <v>2.1565</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2462</v>
+        <v>0.5921</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0786</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7988</v>
+        <v>0.5451</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2113</v>
+        <v>-0.8109</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0101</v>
+        <v>1.356</v>
       </c>
       <c r="V15" t="n">
         <v>1.506</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8326</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3826</v>
+        <v>-1.0723</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2152</v>
+        <v>0.1493</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2434</v>
+        <v>-1.4814</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0465</v>
+        <v>0.4556</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1969</v>
+        <v>-1.937</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2466</v>
+        <v>0.1329</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8784</v>
+        <v>0.6962</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6318</v>
+        <v>-0.5633</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9967</v>
+        <v>-1.6142</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1681</v>
+        <v>-0.2406</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8286</v>
+        <v>-1.3737</v>
       </c>
       <c r="P16" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.7463</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5883</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6292</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.6119</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.9702</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.1287</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.0935</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.0352</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.506</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9317</v>
+        <v>-1.2866</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2339</v>
+        <v>-1.5342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3021</v>
+        <v>0.2476</v>
       </c>
       <c r="G17" t="n">
         <v>0.0643</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7398</v>
+        <v>0.385</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0595</v>
+        <v>-0.3598</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7993</v>
+        <v>0.7447</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3776</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3412</v>
+        <v>-1.4406</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2725</v>
+        <v>0.8283</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0687</v>
+        <v>-2.269</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4814</v>
+        <v>-1.4417</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4556</v>
+        <v>1.4813</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.937</v>
+        <v>-2.923</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1329</v>
+        <v>1.6865</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6962</v>
+        <v>2.9577</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5633</v>
+        <v>-1.2712</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6142</v>
+        <v>-3.1281</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2406</v>
+        <v>-1.4764</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3737</v>
+        <v>-1.6517</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.5821</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.1642</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.7463</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.17</v>
+        <v>-0.1273</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2412</v>
+        <v>-0.4044</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4112</v>
+        <v>0.2771</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6119</v>
+        <v>0.5164</v>
       </c>
       <c r="W18" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.6119</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4228</v>
+        <v>-1.5788</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6281</v>
+        <v>-0.4181</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0509</v>
+        <v>-1.1607</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4417</v>
+        <v>-2.2434</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4813</v>
+        <v>-2.0465</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.923</v>
+        <v>-0.1969</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6865</v>
+        <v>-1.2466</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9577</v>
+        <v>-1.8784</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2712</v>
+        <v>0.6318</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1281</v>
+        <v>-0.9967</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4764</v>
+        <v>-0.1681</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6517</v>
+        <v>-0.8286</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1095</v>
+        <v>0.3824</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6046</v>
+        <v>0.2927</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4951</v>
+        <v>0.0897</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5164</v>
+        <v>0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5164</v>
+        <v>1.506</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4853</v>
+        <v>-1.7674</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7647</v>
+        <v>0.3192</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7206</v>
+        <v>-2.0865</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8831</v>
+        <v>-3.567</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9204</v>
+        <v>-1.422</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9626</v>
+        <v>-2.145</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6334</v>
+        <v>-1.3847</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6385</v>
+        <v>-0.7579</v>
       </c>
       <c r="L20" t="n">
-        <v>0.005</v>
+        <v>-0.6267</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2496</v>
+        <v>-2.1823</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.282</v>
+        <v>-0.6641</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9677</v>
+        <v>-1.5183</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8739</v>
+        <v>-0.7063</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0329</v>
+        <v>-0.832</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.159</v>
+        <v>0.1256</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3299</v>
+        <v>2.1179</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3299</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6494</v>
+        <v>-2.0224</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1813</v>
+        <v>-1.4654</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4681</v>
+        <v>-0.5571</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.567</v>
+        <v>-2.8831</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.422</v>
+        <v>-1.9204</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.145</v>
+        <v>-0.9626</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3847</v>
+        <v>-0.6334</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7579</v>
+        <v>-0.6385</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6267</v>
+        <v>0.005</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1823</v>
+        <v>-2.2496</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6641</v>
+        <v>-1.282</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5183</v>
+        <v>-0.9677</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5884</v>
+        <v>0.3367</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3325</v>
+        <v>0.3322</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2559</v>
+        <v>0.0045</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1179</v>
+        <v>0.3299</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.192</v>
+        <v>-2.801</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4597</v>
+        <v>-0.2595</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7323</v>
+        <v>-2.5415</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3306</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6972</v>
+        <v>-0.3062</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4229</v>
+        <v>-0.2227</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2743</v>
+        <v>-0.0835</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6119</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4247</v>
+        <v>-3.2062</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5967</v>
+        <v>-0.2964</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8279</v>
+        <v>-2.9097</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9129</v>
@@ -2248,13 +2248,13 @@
         <v>0.3881</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3461</v>
+        <v>-0.1276</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6662</v>
+        <v>-0.3659</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3201</v>
+        <v>0.2384</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5537</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.2774</v>
+        <v>-12.2773</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.742</v>
+        <v>-1.7419</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.5354</v>
+        <v>-10.5355</v>
       </c>
       <c r="G24" t="n">
         <v>-13.8744</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.9741</v>
+        <v>-2.974099999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-10.9001</v>
@@ -2302,7 +2302,7 @@
         <v>4.6626</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1885</v>
+        <v>3.188499999999999</v>
       </c>
       <c r="L24" t="n">
         <v>1.474</v>
@@ -2326,13 +2326,13 @@
         <v>9.701600000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9699999999999998</v>
+        <v>0.9701</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.4118</v>
+        <v>-2.411799999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3818</v>
+        <v>3.3817</v>
       </c>
       <c r="V24" t="n">
         <v>1.5972</v>
